--- a/picks.xlsx
+++ b/picks.xlsx
@@ -1,81 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e2daab8ffa038972/Desktop/Fantasy Cricket/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_2B59D2BFD3A0532D139A281159FD083044D3E30A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9BECD4F-BBB2-44D5-BAC9-4871DC0B4AD0}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="480" windowWidth="17280" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>username</t>
-  </si>
-  <si>
-    <t>latestp1</t>
-  </si>
-  <si>
-    <t>latestp2</t>
-  </si>
-  <si>
-    <t>latestp3</t>
-  </si>
-  <si>
-    <t>latestp4</t>
-  </si>
-  <si>
-    <t>latestpw</t>
-  </si>
-  <si>
-    <t>ava</t>
-  </si>
-  <si>
-    <t>jenny</t>
-  </si>
-  <si>
-    <t>sue</t>
-  </si>
-  <si>
-    <t>joanna</t>
-  </si>
-  <si>
-    <t>katie</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -90,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -414,68 +420,350 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>username</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>latestp1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>latestp2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>latestp3</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>latestp4</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>latestpw</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>July2025p1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>July2025p2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>July2025p3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>July2025p4</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>July2025pw</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>July2025_score</t>
+        </is>
+      </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>6</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ava</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Jenny Sparrow</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Katie Dagostino</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Aisling O'Kelly</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Karina Bell</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beth Dimond</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Jenny Sparrow</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Katie Dagostino</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Aisling O'Kelly</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Karina Bell</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Beth Dimond</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>3548</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>7</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>jenny</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Tash Richardson</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Isabella Merriman</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Aisling O'Kelly</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Eimear Richardson</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Katie Dagostino</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tash Richardson</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Isabella Merriman</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Aisling O'Kelly</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Eimear Richardson</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Katie Dagostino</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>2649</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sue</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ava Canning</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Nazli Leetch</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Leah Mullett</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Vida Reynolds</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Valmai Gee</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ava Canning</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Nazli Leetch</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Leah Mullett</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Vida Reynolds</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Valmai Gee</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>joanna</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>10</v>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>katie</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Joanna Loughran</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Olivia Pacitto</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Lauren Torpey</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Eimear Richardson</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ava McCormack</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Joanna Loughran</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Olivia Pacitto</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Lauren Torpey</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Eimear Richardson</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Ava McCormack</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>2627</v>
       </c>
     </row>
   </sheetData>

--- a/picks.xlsx
+++ b/picks.xlsx
@@ -461,32 +461,32 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>July2025p1</t>
+          <t>May2025p1</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>July2025p2</t>
+          <t>May2025p2</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>July2025p3</t>
+          <t>May2025p3</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>July2025p4</t>
+          <t>May2025p4</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>July2025pw</t>
+          <t>May2025pw</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>July2025_score</t>
+          <t>May2025_score</t>
         </is>
       </c>
     </row>
@@ -496,58 +496,38 @@
           <t>ava</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Jenny Sparrow</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Katie Dagostino</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Aisling O'Kelly</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Karina Bell</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Beth Dimond</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Jenny Sparrow</t>
+          <t>Orla Bagnall</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Katie Dagostino</t>
+          <t>Isabella Merriman</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Aisling O'Kelly</t>
+          <t>Anna Delany</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Karina Bell</t>
+          <t>Vida Reynolds</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Beth Dimond</t>
+          <t>Amy Kenealy</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3548</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="3">
@@ -556,58 +536,38 @@
           <t>jenny</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Tash Richardson</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Jenny Sparrow</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>Isabella Merriman</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Aisling O'Kelly</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Ursula Oliver</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>Eimear Richardson</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Katie Dagostino</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Tash Richardson</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Isabella Merriman</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Aisling O'Kelly</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Eimear Richardson</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Katie Dagostino</t>
+          <t>Katie Dillon</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2649</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="4">
@@ -616,56 +576,16 @@
           <t>sue</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ava Canning</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Nazli Leetch</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Leah Mullett</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Vida Reynolds</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Valmai Gee</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Ava Canning</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Nazli Leetch</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Leah Mullett</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Vida Reynolds</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Valmai Gee</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -674,31 +594,11 @@
           <t>joanna</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -712,58 +612,38 @@
           <t>katie</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sophie MacMahon</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Nazli Leetch</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Anna Delany</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Karina Bell</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>Joanna Loughran</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Olivia Pacitto</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Lauren Torpey</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Eimear Richardson</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Ava McCormack</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Joanna Loughran</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Olivia Pacitto</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Lauren Torpey</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Eimear Richardson</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Ava McCormack</t>
-        </is>
-      </c>
       <c r="L6" t="n">
-        <v>2627</v>
+        <v>3024</v>
       </c>
     </row>
   </sheetData>

--- a/picks.xlsx
+++ b/picks.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:X8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,6 +489,66 @@
           <t>May2025_score</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>June2025p1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>June2025p2</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>June2025p3</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>June2025p4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>June2025pw</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>June2025_score</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>July2025p1</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>July2025p2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>July2025p3</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>July2025p4</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>July2025pw</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>July2025_score</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -496,38 +556,94 @@
           <t>ava</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tash Richardson</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Ava McCormack</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Lauren Torpey</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Eimear Richardson</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Rebecca Rolfe</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Orla Bagnall</t>
+          <t>Jenny Sparrow</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Isabella Merriman</t>
+          <t>Ella McMahon</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Anna Delany</t>
+          <t>Ursula Oliver</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Vida Reynolds</t>
+          <t>Karina Bell</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Amy Kenealy</t>
+          <t>Lauren Torpey</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1870</v>
+        <v>4464</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Tash Richardson</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Ava McCormack</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Lauren Torpey</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Eimear Richardson</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Rebecca Rolfe</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>2972</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -536,19 +652,39 @@
           <t>jenny</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ava Canning</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Nazli Leetch</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Zara Deacon</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Lorraine Bagnall</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Aisling O'Kelly</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Jenny Sparrow</t>
+          <t>Isabel Saeed-Maguire</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Isabella Merriman</t>
+          <t>Sharon Moffatt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -558,16 +694,52 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Eimear Richardson</t>
+          <t>Saoirse McGarry</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Katie Dillon</t>
+          <t>Abbie Melia</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3360</v>
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Ava Canning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Nazli Leetch</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Zara Deacon</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lorraine Bagnall</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Aisling O'Kelly</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>1045.5</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -576,17 +748,95 @@
           <t>sue</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Joanna Loughran</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Isabella Merriman</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Anna Delany</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Anna Payet</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Margaret O'Donoghue</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Rebecca Rolfe</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Isabella Merriman</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Leah Mullett</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Caoimhe O'Brien</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Tara Halligan</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Joanna Loughran</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Isabella Merriman</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Anna Delany</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Anna Payet</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Margaret O'Donoghue</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>1495</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -594,17 +844,95 @@
           <t>joanna</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ava Canning</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Beth Dimond</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Anna Delany</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Rachel Sparrow</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Orla Bagnall</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Isabel Saeed-Maguire</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sue O'Connor</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Aisling O'Kelly</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Tara Halligan</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Olivia Pacitto</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Ava Canning</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Beth Dimond</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Anna Delany</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rachel Sparrow</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Orla Bagnall</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -612,38 +940,306 @@
           <t>katie</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rebecca Rolfe</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Sue O'Connor</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Aisling O'Kelly</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Caoimhe O'Brien</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ella McMahon</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>Katie Dillon</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Isabella Merriman</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Lauren Torpey</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Abbie Melia</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Lorraine Bagnall</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Rebecca Rolfe</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Sue O'Connor</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Aisling O'Kelly</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Caoimhe O'Brien</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Ella McMahon</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>alison</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Sophie MacMahon</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Nazli Leetch</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Anna Delany</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ava McCormack</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Ava Deacon</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Helen O'Kelly</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rachel Sparrow</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Orla Bagnall</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Beth Dimond</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Zara Deacon</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>Karina Bell</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Joanna Loughran</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>3024</v>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Margaret O'Donoghue</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Sophie MacMahon</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Ava McCormack</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Ava Deacon</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Helen O'Kelly</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Rachel Sparrow</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>orla</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ava Canning</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Olivia Pacitto</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Ursula Oliver</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Anna Payet</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Isabella Merriman</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Jenny Sparrow</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Katie Dagostino</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sinead O'Shea</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Margaret O'Donoghue</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Sue O'Connor</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Ava Canning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Olivia Pacitto</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Ursula Oliver</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Anna Payet</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Isabella Merriman</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>2114.5</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Laura Delany</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Beth Dimond</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ursula Oliver</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Karina Bell</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Jenny Sparrow</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>3985</v>
       </c>
     </row>
   </sheetData>

--- a/picks.xlsx
+++ b/picks.xlsx
@@ -829,13 +829,33 @@
       <c r="R4" t="n">
         <v>1495</v>
       </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Orla Bagnall</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Amy Kenealy</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ava Deacon</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Tara Halligan</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Isabella Merriman</t>
+        </is>
+      </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="5">

--- a/picks.xlsx
+++ b/picks.xlsx
@@ -637,13 +637,33 @@
       <c r="R2" t="n">
         <v>2972</v>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Ava Canning</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Amy Kenealy</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Ursula Oliver</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Alison Crawford</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Tash Richardson</t>
+        </is>
+      </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="3">
@@ -1041,13 +1061,33 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Alex Sheedy</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Ava McCormack</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Leah Mullett</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Daphne Deacon</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ava Canning</t>
+        </is>
+      </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="7">
